--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.21592967217606</v>
+        <v>11.41008857172861</v>
       </c>
       <c r="D2" t="n">
-        <v>70.31881900733384</v>
+        <v>11.42680808869175</v>
       </c>
       <c r="E2" t="n">
-        <v>15.52009606062086</v>
+        <v>2.52201560985089</v>
       </c>
       <c r="F2" t="n">
-        <v>15.34000950714658</v>
+        <v>2.492751544911319</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.92866325987825</v>
+        <v>4.213407779730215</v>
       </c>
       <c r="D3" t="n">
-        <v>25.9480631036021</v>
+        <v>4.216560254335342</v>
       </c>
       <c r="E3" t="n">
-        <v>15.52009606062086</v>
+        <v>2.52201560985089</v>
       </c>
       <c r="F3" t="n">
-        <v>15.34000950714658</v>
+        <v>2.492751544911319</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.20488960566124</v>
+        <v>8.158294560919952</v>
       </c>
       <c r="D4" t="n">
-        <v>50.79128507640826</v>
+        <v>8.253583824916344</v>
       </c>
       <c r="E4" t="n">
-        <v>15.52009606062086</v>
+        <v>2.52201560985089</v>
       </c>
       <c r="F4" t="n">
-        <v>15.34000950714658</v>
+        <v>2.492751544911319</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.40045187421718</v>
+        <v>9.490073429560292</v>
       </c>
       <c r="D5" t="n">
-        <v>58.90040728996123</v>
+        <v>9.5713161846187</v>
       </c>
       <c r="E5" t="n">
-        <v>15.52009606062086</v>
+        <v>2.52201560985089</v>
       </c>
       <c r="F5" t="n">
-        <v>15.34000950714658</v>
+        <v>2.492751544911319</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.93906267029672</v>
+        <v>10.55259768392322</v>
       </c>
       <c r="D6" t="n">
-        <v>63.44069767988399</v>
+        <v>10.30911337298115</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52009606062086</v>
+        <v>2.52201560985089</v>
       </c>
       <c r="F6" t="n">
-        <v>15.34000950714658</v>
+        <v>2.492751544911319</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
